--- a/MS_Excel_Practical_Exam_Medium_Level da19 mt.xlsx
+++ b/MS_Excel_Practical_Exam_Medium_Level da19 mt.xlsx
@@ -5,22 +5,30 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASDC27\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Library2\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A3D38D3-3358-4594-89BD-4A9BF0B816F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{918A299B-481F-4D6F-A7A8-C0ABD66600F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
-    <sheet name="Sales_Data" sheetId="2" r:id="rId2"/>
-    <sheet name="Product_Master" sheetId="3" r:id="rId3"/>
-    <sheet name="Student_Marks" sheetId="4" r:id="rId4"/>
-    <sheet name="Questions" sheetId="5" r:id="rId5"/>
-    <sheet name="Sheet1" sheetId="6" r:id="rId6"/>
+    <sheet name="pivott table" sheetId="8" r:id="rId2"/>
+    <sheet name="Sales_Data" sheetId="2" r:id="rId3"/>
+    <sheet name="Product_Master" sheetId="3" r:id="rId4"/>
+    <sheet name="Student_Marks" sheetId="4" r:id="rId5"/>
+    <sheet name="Questions" sheetId="5" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId7"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Sheet1!$N$13:$O$19</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="4" r:id="rId8"/>
+    <pivotCache cacheId="8" r:id="rId9"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +44,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -58,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="106">
   <si>
     <t>Total Questions: 30</t>
   </si>
@@ -300,9 +308,6 @@
     <t>EAST</t>
   </si>
   <si>
-    <t>WEST</t>
-  </si>
-  <si>
     <t>NORTH</t>
   </si>
   <si>
@@ -322,6 +327,63 @@
   </si>
   <si>
     <t>MONTH NAME</t>
+  </si>
+  <si>
+    <t>east</t>
+  </si>
+  <si>
+    <t>average marks</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>topper</t>
+  </si>
+  <si>
+    <t>attendance</t>
+  </si>
+  <si>
+    <t>eligibility</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of Unit_Price</t>
+  </si>
+  <si>
+    <t>Sum of Excel</t>
+  </si>
+  <si>
+    <t>median stat.</t>
+  </si>
+  <si>
+    <t>name.id</t>
+  </si>
+  <si>
+    <t>sales person first 2</t>
+  </si>
+  <si>
+    <t>region</t>
+  </si>
+  <si>
+    <t>laptop order</t>
+  </si>
+  <si>
+    <t>north</t>
+  </si>
+  <si>
+    <t>:D9</t>
+  </si>
+  <si>
+    <t>round</t>
+  </si>
+  <si>
+    <t>salesperson name</t>
   </si>
 </sst>
 </file>
@@ -363,11 +425,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -383,6 +452,2537 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[MS_Excel_Practical_Exam_Medium_Level da19 mt.xlsx]pivott table!PivotTable1</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'pivott table'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'pivott table'!$A$4:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Laptop</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Mobile</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Tablet</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'pivott table'!$B$4:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>135000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6B1F-4527-949C-11E954C0B64A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="1988078944"/>
+        <c:axId val="1601709168"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1988078944"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1601709168"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1601709168"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1988078944"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[MS_Excel_Practical_Exam_Medium_Level da19 mt.xlsx]Student_Marks!PivotTable3</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:shade val="51000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="80000">
+                <a:schemeClr val="accent1">
+                  <a:shade val="93000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:shade val="94000"/>
+                  <a:satMod val="135000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="16200000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="diamond"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:shade val="51000"/>
+                    <a:satMod val="130000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="80000">
+                  <a:schemeClr val="accent1">
+                    <a:shade val="93000"/>
+                    <a:satMod val="130000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:shade val="94000"/>
+                    <a:satMod val="135000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="16200000" scaled="0"/>
+            </a:gradFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="35000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+            <a:scene3d>
+              <a:camera prst="orthographicFront">
+                <a:rot lat="0" lon="0" rev="0"/>
+              </a:camera>
+              <a:lightRig rig="threePt" dir="t">
+                <a:rot lat="0" lon="0" rev="1200000"/>
+              </a:lightRig>
+            </a:scene3d>
+            <a:sp3d>
+              <a:bevelT w="63500" h="25400"/>
+            </a:sp3d>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Student_Marks!$B$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:shade val="51000"/>
+                    <a:satMod val="130000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="80000">
+                  <a:schemeClr val="accent1">
+                    <a:shade val="93000"/>
+                    <a:satMod val="130000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:shade val="94000"/>
+                    <a:satMod val="135000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="16200000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="35000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+            <a:scene3d>
+              <a:camera prst="orthographicFront">
+                <a:rot lat="0" lon="0" rev="0"/>
+              </a:camera>
+              <a:lightRig rig="threePt" dir="t">
+                <a:rot lat="0" lon="0" rev="1200000"/>
+              </a:lightRig>
+            </a:scene3d>
+            <a:sp3d>
+              <a:bevelT w="63500" h="25400"/>
+            </a:sp3d>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Student_Marks!$A$13:$A$18</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Arjun</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Pooja</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Rahul</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Sneha</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Vikas</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Student_Marks!$B$13:$B$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>58</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3632-4BF8-8162-8F7F6B6FBB68}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="115"/>
+        <c:overlap val="-20"/>
+        <c:axId val="1988083120"/>
+        <c:axId val="1832381008"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1988083120"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+                <a:alpha val="54000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1832381008"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1832381008"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1988083120"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="222">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>14287</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>90487</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA77FAF9-620D-EA41-0875-1FA8DB329C04}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>185737</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>71437</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2082CB19-78C4-7F4A-E216-4A41CA86924B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Library2" refreshedDate="46216.579831944444" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="6" xr:uid="{B2F3F002-B3E8-4047-9A0D-54E95FB584DE}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:G7" sheet="Sales_Data"/>
+  </cacheSource>
+  <cacheFields count="7">
+    <cacheField name="Order_ID" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="301" maxValue="306"/>
+    </cacheField>
+    <cacheField name="Region" numFmtId="0">
+      <sharedItems count="4">
+        <s v="North"/>
+        <s v="South"/>
+        <s v="East"/>
+        <s v="West"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Salesperson" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Product" numFmtId="0">
+      <sharedItems count="3">
+        <s v="Laptop"/>
+        <s v="Mobile"/>
+        <s v="Tablet"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Quantity" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="5"/>
+    </cacheField>
+    <cacheField name="Unit_Price" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="15000" maxValue="45000"/>
+    </cacheField>
+    <cacheField name="Sales_Date" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Library2" refreshedDate="46216.585450694445" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="5" xr:uid="{B2FE57C3-CE93-48C4-B474-CAD4DB38F099}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:J6" sheet="Student_Marks"/>
+  </cacheSource>
+  <cacheFields count="10">
+    <cacheField name="Student_ID" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="5"/>
+    </cacheField>
+    <cacheField name="Name" numFmtId="0">
+      <sharedItems count="5">
+        <s v="Rahul"/>
+        <s v="Sneha"/>
+        <s v="Arjun"/>
+        <s v="Pooja"/>
+        <s v="Vikas"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Maths" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="55" maxValue="92"/>
+    </cacheField>
+    <cacheField name="Statistics" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="60" maxValue="91"/>
+    </cacheField>
+    <cacheField name="Excel" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="58" maxValue="94"/>
+    </cacheField>
+    <cacheField name="Attendance_%" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="80" maxValue="98"/>
+    </cacheField>
+    <cacheField name="average marks" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="57.666666666666664" maxValue="91.666666666666671"/>
+    </cacheField>
+    <cacheField name="topper" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="attendance" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="3" maxValue="3"/>
+    </cacheField>
+    <cacheField name="eligibility" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="6">
+  <r>
+    <n v="301"/>
+    <x v="0"/>
+    <s v="Amit"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="45000"/>
+    <s v="05-01-2025"/>
+  </r>
+  <r>
+    <n v="302"/>
+    <x v="1"/>
+    <s v="Riya"/>
+    <x v="1"/>
+    <n v="5"/>
+    <n v="15000"/>
+    <s v="07-01-2025"/>
+  </r>
+  <r>
+    <n v="303"/>
+    <x v="2"/>
+    <s v="Kunal"/>
+    <x v="2"/>
+    <n v="3"/>
+    <n v="18000"/>
+    <s v="10-01-2025"/>
+  </r>
+  <r>
+    <n v="304"/>
+    <x v="3"/>
+    <s v="Neha"/>
+    <x v="0"/>
+    <n v="1"/>
+    <n v="45000"/>
+    <s v="12-01-2025"/>
+  </r>
+  <r>
+    <n v="305"/>
+    <x v="0"/>
+    <s v="Amit"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="15000"/>
+    <s v="15-01-2025"/>
+  </r>
+  <r>
+    <n v="306"/>
+    <x v="1"/>
+    <s v="Riya"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="45000"/>
+    <s v="18-01-2025"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="5">
+  <r>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="78"/>
+    <n v="82"/>
+    <n v="85"/>
+    <n v="92"/>
+    <n v="81.666666666666671"/>
+    <s v="Pooja"/>
+    <n v="3"/>
+    <s v="eligible"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <x v="1"/>
+    <n v="88"/>
+    <n v="91"/>
+    <n v="90"/>
+    <n v="96"/>
+    <n v="89.666666666666671"/>
+    <m/>
+    <m/>
+    <s v="eligible"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <x v="2"/>
+    <n v="65"/>
+    <n v="70"/>
+    <n v="72"/>
+    <n v="85"/>
+    <n v="69"/>
+    <m/>
+    <m/>
+    <s v="eligible"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <x v="3"/>
+    <n v="92"/>
+    <n v="89"/>
+    <n v="94"/>
+    <n v="98"/>
+    <n v="91.666666666666671"/>
+    <m/>
+    <m/>
+    <s v="eligible"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <x v="4"/>
+    <n v="55"/>
+    <n v="60"/>
+    <n v="58"/>
+    <n v="80"/>
+    <n v="57.666666666666664"/>
+    <m/>
+    <m/>
+    <s v="not eligibile"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FBAFE3C7-A6FE-4C68-A259-6CB93C1AFE67}" name="PivotTable2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A12:B17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="7">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Unit_Price" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EE46D7AF-22C4-4B4B-B408-A048E31A5C3E}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="7">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Unit_Price" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8EFB992B-F20F-429A-8296-A548FF10E821}" name="PivotTable3" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+  <location ref="A12:B18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Excel" fld="4" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -704,9 +3304,130 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5713B541-7B96-4FBA-A8E3-F9DA77147999}">
+  <dimension ref="A2:B17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="5">
+        <v>135000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="5">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="5">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="5">
+        <v>183000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="5">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="5">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="5">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="5">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" s="5">
+        <v>183000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="7" width="10.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -874,7 +3595,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -928,12 +3649,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>31</v>
       </c>
@@ -952,8 +3680,23 @@
       <c r="F1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I1" t="s">
+        <v>91</v>
+      </c>
+      <c r="J1" t="s">
+        <v>92</v>
+      </c>
+      <c r="K1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -972,8 +3715,28 @@
       <c r="F2">
         <v>92</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2">
+        <f>AVERAGE(C2:E2)</f>
+        <v>81.666666666666671</v>
+      </c>
+      <c r="H2" t="str">
+        <f>INDEX(B2:B6,MATCH(MAX(G2:G6),G2:G6,0))</f>
+        <v>Pooja</v>
+      </c>
+      <c r="I2">
+        <f>COUNTIF(F2:F6,"&gt;90")</f>
+        <v>3</v>
+      </c>
+      <c r="J2" t="str" cm="1">
+        <f t="array" ref="J2:J6">IF(F2:F6&gt;=85,"eligible","not eligibile")</f>
+        <v>eligible</v>
+      </c>
+      <c r="K2" t="str">
+        <f>_xlfn.CONCAT(A2," ",B2)</f>
+        <v>1 Rahul</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -992,8 +3755,19 @@
       <c r="F3">
         <v>96</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3">
+        <f t="shared" ref="G3:G6" si="0">AVERAGE(C3:E3)</f>
+        <v>89.666666666666671</v>
+      </c>
+      <c r="J3" t="str">
+        <v>eligible</v>
+      </c>
+      <c r="K3" t="str">
+        <f t="shared" ref="K3:K6" si="1">_xlfn.CONCAT(A3," ",B3)</f>
+        <v>2 Sneha</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1012,8 +3786,19 @@
       <c r="F4">
         <v>85</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4">
+        <f t="shared" si="0"/>
+        <v>69</v>
+      </c>
+      <c r="J4" t="str">
+        <v>eligible</v>
+      </c>
+      <c r="K4" t="str">
+        <f t="shared" si="1"/>
+        <v>3 Arjun</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1032,8 +3817,19 @@
       <c r="F5">
         <v>98</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5">
+        <f t="shared" si="0"/>
+        <v>91.666666666666671</v>
+      </c>
+      <c r="J5" t="str">
+        <v>eligible</v>
+      </c>
+      <c r="K5" t="str">
+        <f t="shared" si="1"/>
+        <v>4 Pooja</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1052,13 +3848,96 @@
       <c r="F6">
         <v>80</v>
       </c>
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>57.666666666666664</v>
+      </c>
+      <c r="J6" t="str">
+        <v>not eligibile</v>
+      </c>
+      <c r="K6" t="str">
+        <f t="shared" si="1"/>
+        <v>5 Vikas</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="C7" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7">
+        <f>MEDIAN(D2:D6)</f>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="5">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="5">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="5">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="5">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="5">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B18" s="5">
+        <v>399</v>
+      </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="ZQmo4mtqJEDP67miWW19bLWJbKbkBQmk6gjKAfXAisMTEP7LLbbA7LuYZerNMxVAbQJ9TM+GvOr3QcX8Wh7tzQ==" saltValue="ezNFpkKxb5HC6HwlNha1Xw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1280,8 +4159,8 @@
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>69</v>
+      <c r="A28">
+        <v>28</v>
       </c>
       <c r="J28">
         <v>2</v>
@@ -1314,14 +4193,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ED0D104-D6E3-45E4-86C3-070A65F1B9A1}">
-  <dimension ref="A1:R21"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:S34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="12.42578125" customWidth="1"/>
     <col min="7" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.85546875" customWidth="1"/>
+    <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.5703125" customWidth="1"/>
+    <col min="17" max="17" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -1337,7 +4222,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1369,16 +4259,28 @@
         <v>75</v>
       </c>
       <c r="K3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>77</v>
       </c>
       <c r="M3" t="s">
+        <v>85</v>
+      </c>
+      <c r="N3" t="s">
         <v>86</v>
       </c>
-      <c r="N3" t="s">
-        <v>87</v>
+      <c r="O3" t="s">
+        <v>83</v>
+      </c>
+      <c r="P3" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="R3" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -1428,8 +4330,23 @@
         <v>LOW</v>
       </c>
       <c r="N4" t="str">
-        <f>TEXT(G4,"mmm")</f>
-        <v>Jan</v>
+        <f>TEXT(G4,"mmmm")</f>
+        <v>January</v>
+      </c>
+      <c r="O4">
+        <v>106200</v>
+      </c>
+      <c r="P4" t="e">
+        <f>INDEX(D4:D9,MATCH(A16,B16:B18,0))</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Q4" t="str">
+        <f>LEFT(C4,(2))</f>
+        <v>Am</v>
+      </c>
+      <c r="R4" cm="1">
+        <f t="array" ref="R4:R9">ROUND(F4:F9,5)</f>
+        <v>45000</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -1474,8 +4391,18 @@
         <v>HIGH</v>
       </c>
       <c r="N5" t="str">
-        <f t="shared" ref="N5:N9" si="4">TEXT(G5,"mmm")</f>
-        <v>Jan</v>
+        <f t="shared" ref="N5:N9" si="4">TEXT(G5,"mmmm")</f>
+        <v>January</v>
+      </c>
+      <c r="O5">
+        <v>106200</v>
+      </c>
+      <c r="Q5" t="str">
+        <f t="shared" ref="Q5:Q9" si="5">LEFT(C5,(2))</f>
+        <v>Ri</v>
+      </c>
+      <c r="R5">
+        <v>15000</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -1521,7 +4448,17 @@
       </c>
       <c r="N6" t="str">
         <f t="shared" si="4"/>
-        <v>Jan</v>
+        <v>January</v>
+      </c>
+      <c r="O6">
+        <v>84000</v>
+      </c>
+      <c r="Q6" t="str">
+        <f t="shared" si="5"/>
+        <v>Ku</v>
+      </c>
+      <c r="R6">
+        <v>18000</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -1567,7 +4504,17 @@
       </c>
       <c r="N7" t="str">
         <f t="shared" si="4"/>
-        <v>Jan</v>
+        <v>January</v>
+      </c>
+      <c r="O7">
+        <v>67200</v>
+      </c>
+      <c r="Q7" t="str">
+        <f t="shared" si="5"/>
+        <v>Ne</v>
+      </c>
+      <c r="R7">
+        <v>45000</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -1613,7 +4560,17 @@
       </c>
       <c r="N8" t="str">
         <f t="shared" si="4"/>
-        <v>Jan</v>
+        <v>January</v>
+      </c>
+      <c r="O8">
+        <v>60480</v>
+      </c>
+      <c r="Q8" t="str">
+        <f t="shared" si="5"/>
+        <v>Am</v>
+      </c>
+      <c r="R8">
+        <v>15000</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -1659,14 +4616,24 @@
       </c>
       <c r="N9" t="str">
         <f t="shared" si="4"/>
-        <v>Jan</v>
+        <v>January</v>
+      </c>
+      <c r="O9">
+        <v>53100</v>
+      </c>
+      <c r="Q9" t="str">
+        <f t="shared" si="5"/>
+        <v>Ri</v>
+      </c>
+      <c r="R9">
+        <v>45000</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J10" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="1">
         <f>SUM(K4:K9)</f>
         <v>477180</v>
       </c>
@@ -1683,6 +4650,13 @@
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
+      <c r="N12" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="H13" s="1" t="s">
@@ -1691,17 +4665,29 @@
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
+      <c r="N13" t="s">
+        <v>7</v>
+      </c>
+      <c r="O13" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="H14" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I14">
         <f>SUMIF(B4:B9,H14,H4:H9)</f>
-        <v>45000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+        <v>54000</v>
+      </c>
+      <c r="N14" t="s">
+        <v>13</v>
+      </c>
+      <c r="O14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -1715,11 +4701,17 @@
         <v>79</v>
       </c>
       <c r="I15">
-        <f t="shared" ref="I15:I17" si="5">SUMIF(B5:B10,H15,H5:H10)</f>
+        <f t="shared" ref="I15:I17" si="6">SUMIF(B5:B10,H15,H5:H10)</f>
         <v>54000</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="N15" t="s">
+        <v>17</v>
+      </c>
+      <c r="O15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -1730,14 +4722,20 @@
         <v>18</v>
       </c>
       <c r="H16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>60000</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N16" t="s">
+        <v>21</v>
+      </c>
+      <c r="O16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -1748,14 +4746,20 @@
         <v>12</v>
       </c>
       <c r="H17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>90000</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N17" t="s">
+        <v>13</v>
+      </c>
+      <c r="O17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -1765,8 +4769,14 @@
       <c r="C18">
         <v>12</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N18" t="s">
+        <v>17</v>
+      </c>
+      <c r="O18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="H19" s="1" t="s">
         <v>49</v>
       </c>
@@ -1774,26 +4784,154 @@
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N19" t="s">
+        <v>13</v>
+      </c>
+      <c r="O19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="H20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I20">
         <f>MAX(K4:K9)</f>
         <v>106200</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="H21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I21">
         <f>MIN(K4:K9)</f>
         <v>53100</v>
       </c>
+      <c r="N21" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1"/>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="H23" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" t="s">
+        <v>100</v>
+      </c>
+      <c r="O23" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N24" t="s">
+        <v>102</v>
+      </c>
+      <c r="O24" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C26" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" t="s">
+        <v>7</v>
+      </c>
+      <c r="E28" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" t="str" cm="1">
+        <f t="array" ref="E29:E32">_xlfn.UNIQUE(C29:C34)</f>
+        <v>Amit</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C30" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Riya</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C31" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Kunal</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D32" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Neha</v>
+      </c>
+    </row>
+    <row r="33" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C34" t="s">
+        <v>16</v>
+      </c>
+      <c r="D34" t="s">
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="N13:O19" xr:uid="{0ED0D104-D6E3-45E4-86C3-070A65F1B9A1}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Laptop"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="1">
+      <customFilters>
+        <customFilter operator="greaterThan" val="1"/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="O4:O9">
+    <sortCondition descending="1" ref="O4:O9"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>